--- a/Intersecciones/excels/PIURA-AYABACA-AYABACA.xlsx
+++ b/Intersecciones/excels/PIURA-AYABACA-AYABACA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,6 +1832,214 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-262959</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>200202</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AYABACA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FRIAS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-4.9292403</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-79.949783</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>200201</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-678598</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>200202</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AYABACA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FRIAS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-4.9915359</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-79.9685222</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>200201</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-519906</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>200202</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AYABACA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FRIAS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-4.9032958</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-79.972841</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>200201</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I-519907</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>200202</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AYABACA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FRIAS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-4.9301828</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-79.8940337</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>200201</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
